--- a/events/Moscow_2021_MAR/Moscow_2021_MAR_Results.xlsx
+++ b/events/Moscow_2021_MAR/Moscow_2021_MAR_Results.xlsx
@@ -604,6 +604,11 @@
           <t>01:35:03.770</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>104760</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -733,6 +738,11 @@
           <t>01:36:20.620</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>97229</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1252,6 +1262,11 @@
           <t>01:07:10.560</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>106866</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1984,6 +1999,11 @@
           <t>00:16:01.630</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2314,6 +2334,11 @@
           <t>00:16:47.730</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>74307</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2768,6 +2793,11 @@
           <t>00:15:52.620</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>49835</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2830,6 +2860,11 @@
           <t>00:16:11.900</t>
         </is>
       </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>49832</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3093,6 +3128,11 @@
           <t>00:13:50.710</t>
         </is>
       </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3892,6 +3932,11 @@
           <t>01:58:29.270</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>74307</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4344,6 +4389,11 @@
           <t>01:54:36.180</t>
         </is>
       </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>71551</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6163,6 +6213,11 @@
           <t>02:11:06.260</t>
         </is>
       </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6805,6 +6860,11 @@
           <t>02:11:22.060</t>
         </is>
       </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>49835</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6867,6 +6927,11 @@
           <t>02:16:39.060</t>
         </is>
       </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>49832</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7252,6 +7317,11 @@
           <t>02:15:01.990</t>
         </is>
       </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7788,6 +7858,11 @@
           <t>01:35:45.460</t>
         </is>
       </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>112065</t>
+        </is>
+      </c>
       <c r="S111" t="inlineStr">
         <is>
           <t>112066</t>
@@ -8076,6 +8151,11 @@
           <t>48163</t>
         </is>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>71570</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8781,6 +8861,11 @@
           <t>02:06:00.150</t>
         </is>
       </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>112356</t>
+        </is>
+      </c>
       <c r="S125" t="inlineStr">
         <is>
           <t>112355</t>
@@ -8992,6 +9077,11 @@
           <t>02:04:42.170</t>
         </is>
       </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
       <c r="S128" t="inlineStr">
         <is>
           <t>64792</t>
@@ -9129,6 +9219,11 @@
       <c r="P130" t="inlineStr">
         <is>
           <t>02:09:02.990</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>85380</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -9364,7 +9459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11281,6 +11376,292 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>BOROS</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>49832</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Alena</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>KOSTROMITINA</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>49833</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ERLINEKOV</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>49835</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>MIRONCHENKO</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>71551</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>GOMES</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>71570</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ricardo</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>COELHO</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>74307</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Matvei</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ZHUKOV</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>85380</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>EPISHIN</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>97229</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Iuliia</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>BABASHINSKAIA</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>104760</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Maja</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>HORVATH</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>106866</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Alina</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>KOVALEVA</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>112065</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>112356</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Alena</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>VERBINA</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Moscow_2021_MAR/Moscow_2021_MAR_Results.xlsx
+++ b/events/Moscow_2021_MAR/Moscow_2021_MAR_Results.xlsx
@@ -2535,6 +2535,11 @@
           <t>00:15:20.800</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6796,6 +6801,11 @@
       <c r="P95" t="inlineStr">
         <is>
           <t>02:08:45.140</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>47779</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11662,6 +11672,28 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Kristina</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Bedec</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
